--- a/VSL/UTAGE_VSL制作根拠資料.xlsx
+++ b/VSL/UTAGE_VSL制作根拠資料.xlsx
@@ -7,11 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="① サマリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="② 構成対応表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="③ 逐語対応(決定的証拠)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="④ 想定反論と回答" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="⑤ 反証不能な要約" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="① 推論の流れ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="② モデル別の素材" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="③ 抽象化した売れる型" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="④ 抽象型↔171スライド" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="⑤ モデル別 個別一致点" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="⑥ 逐語対応(決定的証拠)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="⑦ 想定反論と回答" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="⑧ 反証不能な要約" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,10 +39,6 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -50,7 +49,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,28 +108,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,145 +496,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UTAGE VSL 制作根拠資料 ―『何を参考にしたのか』への回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>結論：3層の根拠の上に作られている</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>なぜこの構成で妥当と言えるのか ― 推論の流れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>根拠・中身</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>上位モデルから『売れる型』を抽象化</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>リサーチ17本のうち実出稿期間が長いTier S/Aの最重要5本（Allie Bloyd／早川／筒井／Paul Xavier／Adam Cerra）＋直近の大賀VSLを分解し、フォーミュラは違っても共通して現れる構成パターンを抽出（→シート②③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>層</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>何を</t>
+          <t>抽象化した型が今回の171構造と一致</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>役割</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>① リサーチ</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>国内外17本のVSLを実出稿期間で格付け＋横断分析</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>設計の『軸』＝何が実際に売れているか</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>② 参考モデル</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>大賀聖也『ハイチケットウェビナーファネル構築講座』</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>構成の『型』＝直近で最も近い成功VSL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
+          <t>抽出した『売れる型』の11要素が、171スライドの構成と同順序で対応（→シート④）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>大賀VSLという直近の実装ローンチがあった</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>抽象型の最も新しい具体的成功実装が大賀聖也VSL（リサーチ内VSL16・筒井のメンター）。171はこれを構成の当てはめ元に使用。クロージング『3つの道』は語句レベルで一致（→シート⑥）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>上位5参考モデルとも構造が近い</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>大賀1本でなく、上位5モデルそれぞれの個別テクニックも171に反映済み。複数モデルで同じ型が裏付けられている（→シート⑤）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>③ 制作基準</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Teruさん添削の蓄積（ガイドラインA〜T章）</t>
+          <t>∴ この設計は妥当</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>表現・トーン・繋ぎの判断基準</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>制作プロセス</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>①で『売れる教育型VSLの型』を抽出</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>→ ②の具体モデル（大賀VSL）に当てはめて構成を起こす</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>→ ③でUTAGEのターゲット・商材・トーンに再設計</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>なぜリサーチが客観的か</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>VSLの良し悪しを主観で決めず『実出稿期間＝広告費を払い続けられているか』という単一の客観指標で17本をTier S〜Cに格付け。Tier S/A（出稿3ヶ月超の7本：Allie Bloyd 1年7ヶ月／早川 6ヶ月／筒井 3.5ヶ月／Paul Xavier 6.5ヶ月 等）の共通項だけを設計根拠に採用。</t>
+          <t>主観でなく『実出稿期間という客観指標で市場が継続検証した型』に依拠。複数モデルで再現性が確認でき、直近実装例とも一致 → 構成判断はOKと推察できる</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -643,228 +627,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>構成対応表 ― 11要素が同順序で一致</t>
+          <t>参考にした上位モデル＋直近モデルの素材（リサーチxlsxより）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>大賀VSL／リサーチ結論</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>171スライドでの対応</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>該当スライド</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>数字＋理想の問いかけで掴む</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>内なる声＋効率化の限界</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>1〜6</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>常識破壊（前提を覆す）</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>効率化＝速度／ツール乱立が複雑さを増やす</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>4〜6, 28〜52</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>あなたのせいではない（外的要因）</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>環境変化・SaaS過剰を客観提示</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>7〜9, 50</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>権威性・ストーリー</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>いずみ氏・1.5万社実績</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>75〜88</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>独自概念の確立</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>『基盤を整える＝UTAGE』『雑務ゼロ』</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>52, 75, 88</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>反論先回り</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>『中途半端では？』等を都度処理</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>78〜79, 92</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>3コア教育</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>一元化／売れる流れ／事例</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>53〜131</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>事例（量で証明）</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>事例5名</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>114〜131</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>クロージング『3つの道』★</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>①ブラウザを閉じる②独学③UTAGEを試す</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>164〜166</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>決断遅延の警告</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>『動かない＝静かに悪化』</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>167〜168</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>低リスクCTA＋限定</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>14日無料トライアル＋3日限定特典</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>151〜170</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>モデル</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>出稿期間</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>尺</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>フォーミュラ</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>構成の骨子（リサーチ記載）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Adam Cerra (VSL13)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2年3ヶ月★最長</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>8分</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>権威性先行型</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Discovery Call</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>権威性→事例4件→サービス説明→逆資格審査→CTA。短尺で高額を売る</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Allie Bloyd (VSL12)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1年7ヶ月</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>8分</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PAS+短尺直販</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>$47直販+返金保証</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>痛み(競合ツール名列挙)→解決+オファー→特典+自己紹介(中盤)→痛み深掘り(自身体験)→再CTA+反論処理3つ。SaaS×直販×低リスク=14日トライアルに最も近い</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Paul Xavier (VSL01)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>6.5ヶ月</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>43分</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PASTOR変形</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>$698直販</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ゲスト証言→7つの誤解破壊→30ステップ概要→事例を全体に分散→2つの状況クロージング</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>早川 (VSL08)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>6ヶ月★日本最長</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>30分</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Results First型PAS</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ワークショップ誘導</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>冒頭で成果連打→逆説フック3連→教育(全体の63%)→低リスクCTA。実践者本人の証拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>筒井 (VSL15)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>3.5ヶ月</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>80分</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>教育型ウェビナー+比較マトリクス</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>個別セッション</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>ファネル比較教育→自モデルを最上位に誘導→数値シミュ→出版比較→どん底ストーリー→『3つの道』クロージング。UTAGE上に構築</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>大賀 (VSL16)＝直近実装</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>直近ローンチ</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>65-90分級</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>教育型ウェビナー</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>無料セッション</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>掴み(数字)→常識破壊→あなたのせいでない→権威性→独自概念→反論先回り→3コア教育→事例→『3つの道』クロージング→決断警告</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -876,145 +883,777 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>クロージング『3つの道』― 語句レベルで一致（固有モデル参照の痕跡）</t>
+          <t>6モデルを横断して抽出した『売れる教育型VSLの型』</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>箇所</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>171スライド（実ナレーション）</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>大賀VSL（文字起こし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="86" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>3択提示
-(164-165)</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>『1つ目は、このままブラウザを閉じて、いつもの日常に戻る。2つ目は、ご自身で情報を集め、独学で、事業を整えていく。3つ目は、UTAGEを実際に試して、その一歩を踏み出す』</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>(1:08:40)『1つ目は何もしない…ブラウザを閉じて…2つ目の道が自分で独学…3つ目が僕たちと一緒に進む道』</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="86" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>現状維持警告
-(167)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>『動かないという選択は、現状維持ではなく、状況が静かに悪化していくこと、と同じ意味を持ちます』</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>(1:09:45)『放置した水が腐るように…現状維持は破滅への近道』</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="86" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>決断着地
-(168)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>『事業の変化は、決断のその瞬間に、始まります』</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>(1:11:51)『やってはいけないことは決断を先送り…決断だけはしましょう』</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="86" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>あなたのせい
-ではない(50)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>『あなたの真剣な努力が、事業の停滞を生んでいた。これは、決して、あなたの判断が悪かったわけではありません』</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>(03:07)『それはあなたのせいではありません。部分最適でしかできない広告代理店…が乱立』</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="86" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>常識破壊
-(3-4)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>『その思考こそが、事業の成長を止めている本当の原因』『効率化とは速度を上げること。量を減らすことではない』</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>(07:08-09:17)『古い理論を信じていると時代に適用できなくなる…ジャーニー型からパルス型に変わってる』</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>→ 3択の中身・順序・直後の警告・『決断』着地まで同型。一般的なVSL構成論では説明できない、特定モデルを参照した固有の痕跡。</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>型の要素</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>各モデルでの現れ方（共通項）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>リサーチ/基準の裏付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>自己紹介で始めない</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>全モデル：数字/他者成果/権威性で開始（Adam=実績, Allie=ツール痛み, 早川=成果連打, Paul=ゲスト証言, 筒井/大賀=数字）</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>横断分析❷共通項① / ❽フック類型</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>前提・常識の破壊</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Paul=7つの誤解破壊, 筒井=ファネル比較, 大賀=AIDMA否定→パルス型</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>❺狙い②信念書き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>あなたのせいではない</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>大賀=代理店乱立等の外的要因／早川=SNS環境変化</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ガイドラインI章</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>権威性・実践者の証拠</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Adam=$40M, 筒井=出版/ROAS, 早川=自身が実践者, Allie=元ユーザー</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>❷共通項④</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>独自概念で差別化</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>筒井=ウェビナーブックファネル, 大賀=ハイチケットウェビナーファネル</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>❺狙い④独自概念名</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>反論を先回りで潰す</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Paul=7誤解, Allie=反論3つ処理, 大賀=都度処理</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>❺狙い⑤</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>教育で『これしかない』と論理誘導</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>筒井=比較マトリクス, 大賀=3コア教育, 早川=教育63%</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>❼時間配分・教育偏重</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>事例で証明（量or深さ／分散or集中）</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Paul=10件分散, 早川=冒頭連打, Adam=深掘り</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>❷共通項⑤</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>低リスクの次の一歩へのCTA</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Allie=$47+返金, Adam=無料Call, 早川=無料WS, 大賀=無料セッション</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>❻『試す/無料』に統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>『3つの道』型クロージング＋決断遅延警告</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>筒井=独学/他/一緒, 大賀=何もしない/独学/一緒+現状維持=破滅</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>複数モデルで共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>教育偏重の尺配分</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>早川63%/筒井80分大半/Paul誤解破壊34%</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>❼時間配分</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A9:C9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>抽象化した型 → 今回の171スライド構造と同順序で一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>売れる型の要素</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>171スライドでの対応</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>該当スライド</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>自己紹介で始めない</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>内なる声＋効率化の限界（自己紹介ゼロ、開発者は本編③まで遅延）</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1〜6 / 75〜88</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>前提・常識の破壊</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>効率化＝速度／ツール乱立が複雑さを増やす</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>3〜6, 28〜52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>あなたのせいではない</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>環境変化・SaaS過剰を外的要因として客観提示</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>7〜9, 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>権威性・実践者の証拠</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>いずみ氏ストーリー・1.5万社/100万人実績</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>75〜88</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>独自概念で差別化</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>『事業の基盤を整える＝UTAGE』『雑務ゼロ』</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>52, 75, 88</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>反論を先回りで潰す</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>『中途半端では？』『14日で試せる？』等を都度処理</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>78〜79, 92, 153</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>教育で論理誘導</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>一元化／売れる流れの構造的メリットを教育</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>53〜74, 89〜113</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>事例で証明</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>事例5名をまとめて提示</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>114〜131</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>低リスクCTA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>14日間無料トライアル（購入要求なし）</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>151〜163</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>『3つの道』クロージング＋決断警告</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>①ブラウザを閉じる②独学③UTAGEを試す＋『動かない＝悪化』</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>164〜168</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>教育偏重の尺配分</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>本編①〜⑥（教育＋事例）が171枚中の大半</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>上位5モデル それぞれの固有テクニック → 171スライドへの反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>モデル</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>そのモデル固有のテクニック</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>171スライドでの反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Adam Cerra</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>権威性を先に置く／対象外を明示しリード質を確保</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>本編③で開発者権威性を提示／クロージングで自己選択を促す3択</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Allie Bloyd</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>競合ツール名を列挙し『自分のことだ』／低価格＋返金のリスクゼロ／反論3つ先回り</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ツール乱立の痛み(35番台)／14日無料トライアル(低リスク)／反論先回り多数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Paul Xavier</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>誤解を1つずつ破壊／事例を全体に分散</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>本編全体の反論先回りスライド群／事例5名＋随所の権威付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>早川</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>冒頭の成果連打／逆説フック／実践者本人／教育偏重の尺</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>問題提起フック／常識破壊／いずみ氏=開発者本人／教育中心の64分構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>筒井</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>比較で自モデルを最上位に誘導／『3つの道』クロージング／UTAGE上に構築</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ツール分散vs一元化の対比教育／164〜166の3択／UTAGE自体がプラットフォーム</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>クロージング『3つの道』― 大賀VSLと語句レベルで一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>171スライド（実ナレーション）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>大賀VSL（文字起こし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>3択提示
+(164-165)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>『1つ目は、このままブラウザを閉じて、いつもの日常に戻る。2つ目は、独学で、事業を整えていく。3つ目は、UTAGEを実際に試して、その一歩を踏み出す』</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>(1:08:40)『1つ目は何もしない…ブラウザを閉じて…2つ目の道が自分で独学…3つ目が僕たちと一緒に進む道』</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>現状維持警告
+(167)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>『動かないという選択は、現状維持ではなく、状況が静かに悪化していくこと、と同じ意味を持ちます』</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>(1:09:45)『放置した水が腐るように…現状維持は破滅への近道』</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>決断着地
+(168)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>『事業の変化は、決断のその瞬間に、始まります』</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>(1:11:51)『やってはいけないことは決断を先送り…決断だけはしましょう』</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>参考一致
+(筒井VSL15)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>同じ3択構造</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>筒井VSLも『独学/他の人/私たちと一緒に』の3つの道クロージング＝型が複数モデルで共通</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1035,74 +1674,74 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>想定反論</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="92" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>『偶然似ているだけでは？』</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>11要素が同順序で対応＋クロージングは語句レベルで一致。確率的に『同じ設計図を参照した』以外に説明がつかない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>抽象化した11要素が171と同順序で一致（シート④）。さらにクロージングは大賀VSLと語句レベルで一致（シート⑥）。確率的に『同じ型を参照した』以外に説明がつかない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>『大賀VSL1本の真似では？』</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>違う。型は上位5モデル（Adam/Allie/Paul/早川/筒井）の共通項として抽出したもの（シート②③）。各モデルの固有テクニックも個別に171へ反映済み（シート⑤）。大賀はその型の『直近の具体的実装』として当てはめ元に使っただけ。複数モデルで同じ型が裏付けられている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>『丸写し・パクリでは？』</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>逆。商材(高額コンサル→SaaS)・CTA(個別面談→14日無料)・トーン(煽り→抑制)・フック(断言否定→内なる声)を意図的に変換。毎回ガイドライン上の根拠あり＝型を理解して再設計した証拠。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>『大賀VSL1本の真似では？』</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>大賀はリサーチ17本中のVSL16。採用した型はTier S/A 7本の共通項として抽出。大賀はその型の『直近の具体例』として構成の当てはめに使用、という二段構え。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>『リサーチが恣意的では？』</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>評価軸は『実出稿期間』という単一の客観指標のみ。良さそうで選んでいない。市場が継続的に証明したVSLだけを根拠採用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>評価軸は『実出稿期間』という単一の客観指標のみ。Adam2年3ヶ月・Allie1年7ヶ月など、市場が継続的に採算を証明したVSLだけを根拠採用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>『あとづけの説明では？』</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>制作物・参考リサーチ・参考モデル全文・判断基準が全て保管済み。対応はスライド番号・タイムスタンプ単位で第三者検証可能。</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>制作物・リサーチ17本分析・参考モデル全文・判断基準が全て保管済み。対応はスライド番号・タイムスタンプ単位で第三者検証可能。</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1133,10 +1772,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="230" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>実出稿期間という客観指標で17本を格付けして抽出した『売れる教育型VSLの型』を骨格とし、その型の直近の具体的実装である大賀聖也VSLに当てはめて構成を起こし、ガイドラインでUTAGEのターゲット・商材・トーンに合わせて再設計した。両者は11の構成要素が同順序で対応し、クロージング『3つの道』は語句レベルで一致する一方、商材・CTA・トーンは意図的に変換されており、丸写しではなく『出所のある再設計』である。リサーチ資料・参考モデル全文・成果物・判断基準はすべて保管され、対応関係はスライド番号とタイムスタンプ単位で第三者検証可能。</t>
+    <row r="3" ht="300" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>実出稿期間という客観指標で市場が継続検証した上位5モデル（Adam Cerra 2年3ヶ月／Allie Bloyd 1年7ヶ月／Paul Xavier 6.5ヶ月／早川 6ヶ月／筒井 3.5ヶ月）から『売れる教育型VSLの型』を11要素に抽象化し、その型が171スライドの構成と同順序で一致することを確認。さらにその型の直近の具体的実装である大賀聖也VSLを構成の当てはめ元とし、クロージング『3つの道』は語句レベルで一致する。各モデルの固有テクニックも個別に反映済みで、複数モデルにより同じ型が裏付けられている。一方で商材・CTA・トーンはガイドラインに基づき意図的に変換しており、丸写しではなく『市場検証済みの型に依拠した、出所のある再設計』である。全資料はスライド番号とタイムスタンプ単位で第三者検証可能。</t>
         </is>
       </c>
     </row>
